--- a/DevOps_AWS_Senior_Tracker_v3.xlsx
+++ b/DevOps_AWS_Senior_Tracker_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE660D4-30D6-4484-B5C2-091C98337361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB2A732-5D27-4686-9335-F1FFB6B22842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -3853,23 +3853,23 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4199,7 +4199,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -4211,7 +4211,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -4223,7 +4223,7 @@
       <c r="H2" s="39"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="44" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="39"/>
@@ -4439,7 +4439,7 @@
       <c r="C15" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="39"/>
@@ -4451,7 +4451,7 @@
       <c r="H17" s="39"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="42" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="39"/>
@@ -4463,7 +4463,7 @@
       <c r="H18" s="39"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="40" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="39"/>
@@ -4475,7 +4475,7 @@
       <c r="H19" s="39"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="42" t="s">
         <v>43</v>
       </c>
       <c r="B20" s="39"/>
@@ -4487,7 +4487,7 @@
       <c r="H20" s="39"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="40" t="s">
         <v>44</v>
       </c>
       <c r="B21" s="39"/>
@@ -4499,7 +4499,7 @@
       <c r="H21" s="39"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="42" t="s">
         <v>45</v>
       </c>
       <c r="B22" s="39"/>
@@ -4511,7 +4511,7 @@
       <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="40" t="s">
         <v>46</v>
       </c>
       <c r="B23" s="39"/>
@@ -4523,7 +4523,7 @@
       <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="42" t="s">
         <v>47</v>
       </c>
       <c r="B24" s="39"/>
@@ -4535,7 +4535,7 @@
       <c r="H24" s="39"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="40" t="s">
         <v>48</v>
       </c>
       <c r="B25" s="39"/>
@@ -4548,6 +4548,9 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A1:H1"/>
@@ -4557,9 +4560,6 @@
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5292,7 +5292,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="44" t="s">
         <v>234</v>
       </c>
       <c r="B14" s="39"/>
